--- a/data/trans_dic/P26-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P26-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que tienen algún familiar que fuma habitualmente en casa</t>
+          <t>Población que tienen algún familiar que fuma habitualmente en casa (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,6; 39,9</t>
+          <t>27,8; 39,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,68; 44,83</t>
+          <t>32,54; 44,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,46; 41,0</t>
+          <t>27,84; 40,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,59; 26,68</t>
+          <t>13,8; 26,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,35; 49,47</t>
+          <t>36,73; 49,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,15; 48,94</t>
+          <t>36,35; 48,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,15; 45,22</t>
+          <t>33,0; 45,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,23; 28,98</t>
+          <t>17,89; 28,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,81; 42,93</t>
+          <t>33,38; 42,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,7; 44,79</t>
+          <t>35,88; 45,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,83; 41,16</t>
+          <t>32,07; 40,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,87; 24,69</t>
+          <t>16,94; 25,23</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,16; 29,38</t>
+          <t>21,44; 29,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,82; 37,0</t>
+          <t>28,12; 37,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,55; 27,24</t>
+          <t>19,24; 26,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 15,41</t>
+          <t>6,29; 15,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,05; 38,33</t>
+          <t>29,72; 38,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,35; 45,23</t>
+          <t>36,6; 45,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,52; 36,9</t>
+          <t>28,67; 37,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,39; 15,83</t>
+          <t>10,01; 15,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,32; 32,56</t>
+          <t>26,51; 32,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,77; 40,02</t>
+          <t>34,03; 40,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,26; 31,13</t>
+          <t>25,3; 31,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 14,16</t>
+          <t>8,77; 13,85</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,95; 32,32</t>
+          <t>22,4; 32,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,55; 41,0</t>
+          <t>30,7; 41,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,99; 22,74</t>
+          <t>14,45; 23,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 9,86</t>
+          <t>4,35; 9,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,2; 43,89</t>
+          <t>33,02; 44,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,9; 41,8</t>
+          <t>30,53; 41,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,11; 17,52</t>
+          <t>9,89; 17,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,11; 19,65</t>
+          <t>12,02; 19,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,26; 36,42</t>
+          <t>29,07; 36,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,89; 39,88</t>
+          <t>31,92; 39,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,77; 18,57</t>
+          <t>13,14; 18,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 13,94</t>
+          <t>9,21; 13,87</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,1; 33,68</t>
+          <t>23,75; 33,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,87; 35,0</t>
+          <t>24,47; 34,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,93; 34,4</t>
+          <t>23,87; 33,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,68; 22,05</t>
+          <t>9,51; 21,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,64; 47,17</t>
+          <t>37,15; 47,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,41; 33,91</t>
+          <t>25,03; 34,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,13; 34,16</t>
+          <t>24,38; 34,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,5</t>
+          <t>5,56; 13,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,76; 38,98</t>
+          <t>31,62; 39,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,15; 32,88</t>
+          <t>26,01; 32,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,06; 32,4</t>
+          <t>25,63; 32,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 14,84</t>
+          <t>8,3; 15,87</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,87; 35,43</t>
+          <t>21,76; 35,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,13; 39,82</t>
+          <t>26,84; 40,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,17; 33,58</t>
+          <t>21,71; 34,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 8,81</t>
+          <t>1,71; 8,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,82; 37,45</t>
+          <t>23,98; 38,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,63; 46,8</t>
+          <t>33,58; 46,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 27,73</t>
+          <t>16,62; 27,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 9,17</t>
+          <t>4,37; 9,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,34; 34,1</t>
+          <t>24,75; 34,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,93; 41,8</t>
+          <t>32,03; 41,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20,14; 28,52</t>
+          <t>20,4; 28,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,89</t>
+          <t>3,84; 7,82</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,89; 34,27</t>
+          <t>22,66; 33,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,79; 36,45</t>
+          <t>24,6; 36,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,73; 29,67</t>
+          <t>18,37; 29,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,58; 15,19</t>
+          <t>7,19; 15,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,85; 46,33</t>
+          <t>33,54; 45,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,39; 50,0</t>
+          <t>37,36; 49,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,39; 36,03</t>
+          <t>24,02; 36,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,58; 15,66</t>
+          <t>8,76; 15,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,73; 38,09</t>
+          <t>29,73; 37,41</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32,57; 41,16</t>
+          <t>32,91; 41,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,1; 30,84</t>
+          <t>23,01; 30,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,17; 14,53</t>
+          <t>8,88; 14,25</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,56; 34,19</t>
+          <t>26,62; 34,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,2; 38,3</t>
+          <t>30,25; 38,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,32; 30,81</t>
+          <t>23,27; 30,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,5; 23,7</t>
+          <t>16,04; 23,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,42; 42,05</t>
+          <t>34,55; 42,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,17; 46,47</t>
+          <t>38,09; 46,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,74; 34,54</t>
+          <t>26,49; 33,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,17; 24,57</t>
+          <t>7,95; 24,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,63; 37,42</t>
+          <t>31,74; 37,58</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35,4; 40,88</t>
+          <t>35,74; 41,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25,79; 31,3</t>
+          <t>25,98; 31,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,84; 22,43</t>
+          <t>11,61; 22,6</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,75; 31,84</t>
+          <t>25,04; 32,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,99; 34,73</t>
+          <t>27,75; 35,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,08; 26,53</t>
+          <t>20,23; 26,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,4; 67,48</t>
+          <t>5,22; 69,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,81; 38,31</t>
+          <t>30,96; 38,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,98; 39,82</t>
+          <t>33,23; 40,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,91; 23,76</t>
+          <t>17,92; 23,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,05</t>
+          <t>4,56; 8,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,36; 34,19</t>
+          <t>29,11; 34,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31,5; 36,52</t>
+          <t>31,54; 36,52</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19,76; 24,16</t>
+          <t>19,56; 24,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,5; 49,63</t>
+          <t>5,71; 57,2</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26,86; 30,13</t>
+          <t>27,03; 30,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,4; 34,62</t>
+          <t>31,31; 34,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23,62; 26,85</t>
+          <t>23,71; 26,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,44; 38,5</t>
+          <t>11,2; 36,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35,32; 38,83</t>
+          <t>35,37; 38,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,15; 40,41</t>
+          <t>36,9; 40,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,12; 28,2</t>
+          <t>25,04; 28,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,37; 14,3</t>
+          <t>10,25; 14,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31,63; 34,08</t>
+          <t>31,63; 34,12</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34,64; 37,1</t>
+          <t>34,58; 37,03</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24,86; 27,16</t>
+          <t>24,91; 27,18</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,95; 26,66</t>
+          <t>11,88; 26,28</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que tienen algún familiar que fuma habitualmente en casa</t>
+          <t>Población que tienen algún familiar que fuma habitualmente en casa (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>67244; 97201</t>
+          <t>67728; 96880</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91793; 125949</t>
+          <t>91407; 125762</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74657; 107572</t>
+          <t>73048; 105861</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36480; 71615</t>
+          <t>37046; 70691</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>84049; 114373</t>
+          <t>84932; 115499</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100191; 135621</t>
+          <t>100738; 135562</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86658; 118226</t>
+          <t>86267; 118360</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46046; 73204</t>
+          <t>45189; 71961</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>160518; 203854</t>
+          <t>158513; 202651</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>199245; 249956</t>
+          <t>200242; 252208</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>166735; 215607</t>
+          <t>167977; 214585</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>87894; 128624</t>
+          <t>88271; 131457</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98962; 137435</t>
+          <t>100270; 137597</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>137224; 182526</t>
+          <t>138696; 185039</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96536; 134522</t>
+          <t>95024; 132872</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29244; 75400</t>
+          <t>30800; 73502</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>134353; 177316</t>
+          <t>137490; 176753</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>185748; 231157</t>
+          <t>187018; 234038</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>145188; 187817</t>
+          <t>145953; 189474</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49521; 75437</t>
+          <t>47711; 74767</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>244897; 302913</t>
+          <t>246619; 302961</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>339110; 401947</t>
+          <t>341742; 404881</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>253278; 312114</t>
+          <t>253705; 312198</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85933; 136807</t>
+          <t>84690; 133815</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>65512; 96471</t>
+          <t>66865; 97210</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92742; 124485</t>
+          <t>93215; 125769</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43040; 69952</t>
+          <t>44440; 71115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13254; 29257</t>
+          <t>12903; 28372</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>101208; 133768</t>
+          <t>100651; 134361</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91604; 128057</t>
+          <t>93523; 126685</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32199; 55812</t>
+          <t>31522; 56604</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39122; 63486</t>
+          <t>38814; 63363</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>176495; 219735</t>
+          <t>175375; 220500</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>194495; 243257</t>
+          <t>194692; 241174</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79961; 116293</t>
+          <t>82305; 118237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>56499; 86368</t>
+          <t>57097; 85971</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>81763; 114270</t>
+          <t>80590; 113919</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87501; 128312</t>
+          <t>89712; 126622</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81097; 116554</t>
+          <t>80898; 115148</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25151; 57313</t>
+          <t>24703; 55412</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>124296; 160029</t>
+          <t>126051; 160352</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>92140; 128004</t>
+          <t>94487; 130342</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84682; 119864</t>
+          <t>85568; 121387</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21829; 56323</t>
+          <t>23198; 58281</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>215481; 264490</t>
+          <t>214589; 265910</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>194566; 244662</t>
+          <t>193573; 244953</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>172857; 223473</t>
+          <t>176767; 226495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53643; 100467</t>
+          <t>56177; 107440</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39197; 63516</t>
+          <t>39008; 63376</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55551; 84674</t>
+          <t>57061; 85192</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41144; 65275</t>
+          <t>42199; 67528</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3160; 14493</t>
+          <t>2817; 14172</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>44655; 70193</t>
+          <t>44945; 72442</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72367; 100703</t>
+          <t>72265; 101094</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35738; 57779</t>
+          <t>34641; 57267</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8762; 18348</t>
+          <t>8753; 18099</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>89255; 125046</t>
+          <t>90749; 126269</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>136582; 178826</t>
+          <t>137015; 178271</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81122; 114875</t>
+          <t>82181; 116618</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14179; 28769</t>
+          <t>13993; 28495</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57413; 85957</t>
+          <t>56843; 85124</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63818; 93828</t>
+          <t>63334; 93081</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44996; 71269</t>
+          <t>44132; 70226</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18913; 37918</t>
+          <t>17951; 37702</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>83923; 114862</t>
+          <t>83155; 112461</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>95029; 127080</t>
+          <t>94955; 126508</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60233; 88987</t>
+          <t>59319; 89235</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21285; 38875</t>
+          <t>21733; 38406</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>148293; 189964</t>
+          <t>148273; 186597</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166634; 210579</t>
+          <t>168355; 212632</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>112527; 150273</t>
+          <t>112121; 150339</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>45655; 72310</t>
+          <t>44224; 70906</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>153231; 197271</t>
+          <t>153572; 198236</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>183673; 232890</t>
+          <t>183930; 232942</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>137510; 181655</t>
+          <t>137228; 181331</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91002; 139127</t>
+          <t>94129; 140249</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>202339; 247219</t>
+          <t>203097; 250512</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>237054; 288626</t>
+          <t>236578; 290219</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>164194; 212034</t>
+          <t>162619; 208655</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>67132; 201991</t>
+          <t>65329; 202434</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>368505; 435949</t>
+          <t>369716; 437746</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>435152; 502425</t>
+          <t>439257; 504938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>310456; 376738</t>
+          <t>312628; 375837</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>166761; 316094</t>
+          <t>163563; 318397</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>172163; 221507</t>
+          <t>174220; 224953</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>212120; 263196</t>
+          <t>210283; 270036</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>145428; 192113</t>
+          <t>146482; 192368</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46153; 576702</t>
+          <t>44598; 594302</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>225287; 280136</t>
+          <t>226419; 280556</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>263993; 318706</t>
+          <t>265946; 321874</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>138616; 183929</t>
+          <t>138709; 184668</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>28608; 50315</t>
+          <t>28498; 50805</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>419005; 487861</t>
+          <t>415450; 486779</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>490855; 569108</t>
+          <t>491450; 569122</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>296013; 361919</t>
+          <t>293083; 362330</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>81341; 734377</t>
+          <t>84471; 846506</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>819766; 919521</t>
+          <t>824973; 926295</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1030129; 1135805</t>
+          <t>1027083; 1135492</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>744248; 846071</t>
+          <t>747042; 847666</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>362671; 1220357</t>
+          <t>354939; 1164886</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1092109; 1200621</t>
+          <t>1093745; 1202815</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1249274; 1358923</t>
+          <t>1240770; 1360887</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>824932; 925972</t>
+          <t>822229; 926247</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>348927; 481007</t>
+          <t>344940; 485998</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1943595; 2094258</t>
+          <t>1943490; 2096193</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2301312; 2464960</t>
+          <t>2297091; 2459735</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1599733; 1747684</t>
+          <t>1603052; 1748846</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>781055; 1741870</t>
+          <t>776418; 1717584</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P26-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P26-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,8; 39,77</t>
+          <t>27,43; 39,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,54; 44,77</t>
+          <t>32,99; 45,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,84; 40,35</t>
+          <t>28,09; 40,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,8; 26,34</t>
+          <t>12,2; 22,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,73; 49,95</t>
+          <t>35,96; 49,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,35; 48,92</t>
+          <t>36,27; 49,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,0; 45,27</t>
+          <t>33,48; 45,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,89; 28,48</t>
+          <t>16,52; 25,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,38; 42,68</t>
+          <t>33,83; 42,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,88; 45,2</t>
+          <t>36,09; 44,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,07; 40,97</t>
+          <t>32,51; 41,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,94; 25,23</t>
+          <t>15,54; 22,01</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,44; 29,42</t>
+          <t>21,6; 30,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,12; 37,51</t>
+          <t>28,35; 37,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,24; 26,91</t>
+          <t>19,11; 27,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,29; 15,02</t>
+          <t>5,84; 14,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,72; 38,21</t>
+          <t>29,59; 37,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,6; 45,8</t>
+          <t>36,81; 45,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,67; 37,22</t>
+          <t>28,75; 37,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,01; 15,69</t>
+          <t>9,57; 15,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,51; 32,57</t>
+          <t>26,32; 32,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,03; 40,31</t>
+          <t>33,71; 39,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,3; 31,13</t>
+          <t>25,25; 30,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,77; 13,85</t>
+          <t>8,6; 13,54</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,4; 32,57</t>
+          <t>22,34; 32,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,7; 41,42</t>
+          <t>30,81; 41,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,45; 23,12</t>
+          <t>14,31; 22,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 9,56</t>
+          <t>5,13; 11,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,02; 44,08</t>
+          <t>32,77; 43,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,53; 41,35</t>
+          <t>30,5; 42,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,89; 17,77</t>
+          <t>9,61; 17,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,02; 19,62</t>
+          <t>11,94; 18,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,07; 36,55</t>
+          <t>28,98; 36,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,92; 39,54</t>
+          <t>31,67; 39,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,14; 18,88</t>
+          <t>13,1; 18,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,87</t>
+          <t>9,47; 14,1</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,75; 33,58</t>
+          <t>24,05; 33,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,47; 34,54</t>
+          <t>24,09; 34,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,87; 33,98</t>
+          <t>24,49; 34,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 21,32</t>
+          <t>9,3; 21,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,15; 47,26</t>
+          <t>36,84; 47,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,03; 34,53</t>
+          <t>25,06; 34,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,38; 34,59</t>
+          <t>24,4; 34,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 13,97</t>
+          <t>9,84; 17,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,62; 39,19</t>
+          <t>31,94; 39,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,01; 32,92</t>
+          <t>26,05; 33,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,63; 32,84</t>
+          <t>25,43; 32,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 15,87</t>
+          <t>10,71; 17,09</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,76; 35,35</t>
+          <t>22,33; 36,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,84; 40,07</t>
+          <t>26,83; 40,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,71; 34,74</t>
+          <t>22,07; 34,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,62</t>
+          <t>2,52; 9,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,98; 38,65</t>
+          <t>23,71; 37,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,58; 46,98</t>
+          <t>34,14; 47,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,62; 27,48</t>
+          <t>17,04; 28,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,05</t>
+          <t>4,39; 9,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,75; 34,43</t>
+          <t>24,66; 33,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32,03; 41,67</t>
+          <t>32,2; 41,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20,4; 28,96</t>
+          <t>20,71; 28,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,82</t>
+          <t>4,09; 7,9</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,66; 33,94</t>
+          <t>22,5; 33,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,6; 36,16</t>
+          <t>24,6; 36,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,37; 29,23</t>
+          <t>18,49; 29,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,19; 15,11</t>
+          <t>8,1; 15,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,54; 45,36</t>
+          <t>33,58; 46,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,36; 49,77</t>
+          <t>37,26; 50,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,02; 36,13</t>
+          <t>23,74; 36,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,76; 15,47</t>
+          <t>8,17; 15,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,73; 37,41</t>
+          <t>29,62; 38,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32,91; 41,56</t>
+          <t>32,5; 41,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,01; 30,86</t>
+          <t>23,12; 30,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,88; 14,25</t>
+          <t>9,28; 14,17</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,62; 34,36</t>
+          <t>26,88; 34,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,25; 38,31</t>
+          <t>30,35; 38,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,27; 30,75</t>
+          <t>23,4; 31,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,04; 23,89</t>
+          <t>15,64; 22,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,55; 42,61</t>
+          <t>34,4; 42,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,09; 46,73</t>
+          <t>38,46; 46,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,49; 33,99</t>
+          <t>26,72; 33,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,95; 24,63</t>
+          <t>19,75; 25,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,74; 37,58</t>
+          <t>31,68; 37,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35,74; 41,08</t>
+          <t>35,33; 41,25</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25,98; 31,23</t>
+          <t>26,06; 31,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,61; 22,6</t>
+          <t>18,54; 23,6</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,04; 32,34</t>
+          <t>25,26; 32,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,75; 35,63</t>
+          <t>28,03; 35,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,23; 26,57</t>
+          <t>20,24; 26,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,22; 69,54</t>
+          <t>4,1; 8,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,96; 38,36</t>
+          <t>31,34; 38,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,23; 40,21</t>
+          <t>33,1; 40,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,92; 23,86</t>
+          <t>17,58; 23,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,13</t>
+          <t>4,4; 7,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,11; 34,11</t>
+          <t>29,19; 33,85</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31,54; 36,52</t>
+          <t>31,64; 36,41</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19,56; 24,18</t>
+          <t>19,92; 24,03</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,71; 57,2</t>
+          <t>4,61; 7,26</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27,03; 30,35</t>
+          <t>26,83; 30,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,31; 34,61</t>
+          <t>31,09; 34,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23,71; 26,9</t>
+          <t>23,72; 26,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,2; 36,75</t>
+          <t>10,21; 12,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35,37; 38,9</t>
+          <t>35,5; 38,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,9; 40,47</t>
+          <t>36,99; 40,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,04; 28,21</t>
+          <t>25,24; 28,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,25; 14,44</t>
+          <t>12,6; 14,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31,63; 34,12</t>
+          <t>31,74; 34,04</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34,58; 37,03</t>
+          <t>34,57; 37,03</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24,91; 27,18</t>
+          <t>24,93; 27,11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,88; 26,28</t>
+          <t>11,78; 13,51</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50887</t>
+          <t>46051</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56707</t>
+          <t>56762</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>107594</t>
+          <t>102813</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>67728; 96880</t>
+          <t>66816; 96550</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91407; 125762</t>
+          <t>92677; 126859</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73048; 105861</t>
+          <t>73700; 106204</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37046; 70691</t>
+          <t>33850; 61193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>84932; 115499</t>
+          <t>83148; 115064</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100738; 135562</t>
+          <t>100522; 136196</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86267; 118360</t>
+          <t>87532; 118147</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45189; 71961</t>
+          <t>45590; 69857</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>158513; 202651</t>
+          <t>160623; 201742</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>200242; 252208</t>
+          <t>201394; 249924</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167977; 214585</t>
+          <t>170274; 215343</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>88271; 131457</t>
+          <t>86014; 121783</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48720</t>
+          <t>46534</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>60527</t>
+          <t>62355</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>109247</t>
+          <t>108890</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>100270; 137597</t>
+          <t>101038; 141104</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>138696; 185039</t>
+          <t>139866; 184337</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95024; 132872</t>
+          <t>94368; 133833</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30800; 73502</t>
+          <t>29150; 71946</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>137490; 176753</t>
+          <t>136872; 174142</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>187018; 234038</t>
+          <t>188089; 234729</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>145953; 189474</t>
+          <t>146322; 190840</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47711; 74767</t>
+          <t>48532; 78121</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>246619; 302961</t>
+          <t>244810; 302416</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>341742; 404881</t>
+          <t>338558; 401547</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>253705; 312198</t>
+          <t>253179; 309873</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>84690; 133815</t>
+          <t>86533; 136278</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50139</t>
+          <t>50247</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69820</t>
+          <t>73613</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>66865; 97210</t>
+          <t>66690; 96211</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93215; 125769</t>
+          <t>93535; 124932</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44440; 71115</t>
+          <t>44023; 68720</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12903; 28372</t>
+          <t>15193; 33540</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100651; 134361</t>
+          <t>99884; 133469</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93523; 126685</t>
+          <t>93452; 129060</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31522; 56604</t>
+          <t>30611; 56277</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38814; 63363</t>
+          <t>39373; 62154</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>175375; 220500</t>
+          <t>174842; 221348</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>194692; 241174</t>
+          <t>193205; 243040</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82305; 118237</t>
+          <t>82052; 117418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57097; 85971</t>
+          <t>59258; 88250</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38153</t>
+          <t>43869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>40046</t>
+          <t>46371</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78199</t>
+          <t>90240</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>80590; 113919</t>
+          <t>81600; 112025</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89712; 126622</t>
+          <t>88310; 125384</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80898; 115148</t>
+          <t>82978; 117322</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24703; 55412</t>
+          <t>28322; 64012</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>126051; 160352</t>
+          <t>124996; 160011</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94487; 130342</t>
+          <t>94582; 130467</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85568; 121387</t>
+          <t>85612; 120425</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23198; 58281</t>
+          <t>35317; 61915</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>214589; 265910</t>
+          <t>216763; 266046</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>193573; 244953</t>
+          <t>193823; 245952</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>176767; 226495</t>
+          <t>175385; 224205</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>56177; 107440</t>
+          <t>71007; 113344</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>23369</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39008; 63376</t>
+          <t>40037; 64630</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>57061; 85192</t>
+          <t>57047; 85814</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42199; 67528</t>
+          <t>42904; 66797</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2817; 14172</t>
+          <t>4785; 17461</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>44945; 72442</t>
+          <t>44445; 70376</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72265; 101094</t>
+          <t>73475; 102221</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34641; 57267</t>
+          <t>35508; 58368</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8753; 18099</t>
+          <t>9633; 20078</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>90749; 126269</t>
+          <t>90435; 124259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>137015; 178271</t>
+          <t>137758; 178176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82181; 116618</t>
+          <t>83402; 116691</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13993; 28495</t>
+          <t>16707; 32326</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>28649</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>29067</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56858</t>
+          <t>57716</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>56843; 85124</t>
+          <t>56441; 85025</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63334; 93081</t>
+          <t>63326; 92851</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44132; 70226</t>
+          <t>44411; 70562</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17951; 37702</t>
+          <t>20364; 39312</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>83155; 112461</t>
+          <t>83239; 114216</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>94955; 126508</t>
+          <t>94712; 127543</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59319; 89235</t>
+          <t>58633; 89191</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21733; 38406</t>
+          <t>20801; 38979</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>148273; 186597</t>
+          <t>147748; 190687</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>168355; 212632</t>
+          <t>166268; 209811</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>112121; 150339</t>
+          <t>112669; 150585</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44224; 70906</t>
+          <t>46924; 71661</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113730</t>
+          <t>127406</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>145531</t>
+          <t>166494</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>259260</t>
+          <t>293901</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>153572; 198236</t>
+          <t>155123; 201490</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>183930; 232942</t>
+          <t>184543; 232837</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>137228; 181331</t>
+          <t>137956; 184945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>94129; 140249</t>
+          <t>105301; 153844</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>203097; 250512</t>
+          <t>202239; 249880</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>236578; 290219</t>
+          <t>238865; 291622</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>162619; 208655</t>
+          <t>164021; 208341</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>65329; 202434</t>
+          <t>145907; 189131</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>369716; 437746</t>
+          <t>369035; 433051</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>439257; 504938</t>
+          <t>434258; 507092</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>312628; 375837</t>
+          <t>313709; 377433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>163563; 318397</t>
+          <t>261735; 333233</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>280587</t>
+          <t>40977</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>38013</t>
+          <t>42451</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>318599</t>
+          <t>83428</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>174220; 224953</t>
+          <t>175762; 223515</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>210283; 270036</t>
+          <t>212455; 268025</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>146482; 192368</t>
+          <t>146560; 192863</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>44598; 594302</t>
+          <t>28996; 58246</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>226419; 280556</t>
+          <t>229176; 280698</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>265946; 321874</t>
+          <t>264936; 323395</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>138709; 184668</t>
+          <t>136053; 184222</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>28498; 50805</t>
+          <t>31917; 55585</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>415450; 486779</t>
+          <t>416469; 483064</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>491450; 569122</t>
+          <t>493001; 567366</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>293083; 362330</t>
+          <t>298424; 360080</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>84471; 846506</t>
+          <t>66088; 104079</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>586260</t>
+          <t>366387</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>433391</t>
+          <t>467580</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1019650</t>
+          <t>833968</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>824973; 926295</t>
+          <t>818869; 923660</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1027083; 1135492</t>
+          <t>1019908; 1131297</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>747042; 847666</t>
+          <t>747300; 845332</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>354939; 1164886</t>
+          <t>326728; 413423</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1093745; 1202815</t>
+          <t>1097897; 1201372</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1240770; 1360887</t>
+          <t>1243776; 1360681</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>822229; 926247</t>
+          <t>828639; 927472</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>344940; 485998</t>
+          <t>429704; 505219</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1943490; 2096193</t>
+          <t>1949927; 2091256</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2297091; 2459735</t>
+          <t>2296675; 2459791</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1603052; 1748846</t>
+          <t>1604204; 1744154</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>776418; 1717584</t>
+          <t>778596; 892654</t>
         </is>
       </c>
     </row>
